--- a/data/trans_bre/P1435_2011_2023-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1435_2011_2023-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>259,28%</t>
+          <t>296,77%</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,1</t>
+          <t>0,32; 3,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 8,35</t>
+          <t>0,51; 8,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-71,33; —</t>
+          <t>-59,61; —</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267,63%</t>
+          <t>415,26%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,04</t>
+          <t>0,97; 3,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,5</t>
+          <t>1,64; 5,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,48; —</t>
+          <t>63,18; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1380,44</t>
+          <t>38,37; 2106,35</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433,64%</t>
+          <t>460,4%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,34</t>
+          <t>1,84; 4,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,1</t>
+          <t>3,36; 7,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>138,0; 1244,64</t>
+          <t>154,56; 1395,09</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>460,15%</t>
+          <t>303,62%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,7</t>
+          <t>3,26; 7,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,24</t>
+          <t>4,91; 8,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>244,76; 3594,46</t>
+          <t>204,85; 3324,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>195,14; 1394,83</t>
+          <t>131,62; 595,28</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>13,38</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>737,47%</t>
+          <t>713,74%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,75</t>
+          <t>4,49; 9,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 15,43</t>
+          <t>10,93; 15,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>224,64; 3790,29</t>
+          <t>268,21; 3569,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>374,68; 1488,46</t>
+          <t>337,15; 1449,34</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38,68</t>
+          <t>9,43</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1420,51%</t>
+          <t>355,24%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,33</t>
+          <t>1,67; 5,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 74,48</t>
+          <t>6,8; 12,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>265,59; 5868,0</t>
+          <t>166,43; 706,6</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>406,46%</t>
+          <t>439,8%</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,75</t>
+          <t>-0,83; 1,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,19</t>
+          <t>4,63; 9,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134,5; 1004,12</t>
+          <t>150,86; 1096,78</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12,25</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>748,43%</t>
+          <t>430,31%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,92</t>
+          <t>2,6; 3,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 27,07</t>
+          <t>6,39; 8,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>489,49; 2014,94</t>
+          <t>503,14; 2297,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>375,82; 1948,0</t>
+          <t>295,79; 611,38</t>
         </is>
       </c>
     </row>
